--- a/questions.xlsx
+++ b/questions.xlsx
@@ -1,34 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="題庫" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="題庫" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
   <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -199,6 +150,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,6 +185,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -267,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -402,91 +351,875 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K23"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" customWidth="1"/>
+    <col min="4" max="4" width="50.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="24.83203125" customWidth="1"/>
+    <col min="11" max="11" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>題型</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>標題</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>題目內容</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>選項A</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>選項B</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>選項C</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>選項D</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>正確答案</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>多組答案(|分隔)</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>圖片網址</t>
-        </is>
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>題型</v>
+      </c>
+      <c r="C1" t="str">
+        <v>標題</v>
+      </c>
+      <c r="D1" t="str">
+        <v>題目內容</v>
+      </c>
+      <c r="E1" t="str">
+        <v>選項A</v>
+      </c>
+      <c r="F1" t="str">
+        <v>選項B</v>
+      </c>
+      <c r="G1" t="str">
+        <v>選項C</v>
+      </c>
+      <c r="H1" t="str">
+        <v>選項D</v>
+      </c>
+      <c r="I1" t="str">
+        <v>正確答案</v>
+      </c>
+      <c r="J1" t="str">
+        <v>多組答案(|分隔)</v>
+      </c>
+      <c r="K1" t="str">
+        <v>圖片網址</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>image-choice</v>
+      </c>
+      <c r="C2" t="str">
+        <v>辨認動物</v>
+      </c>
+      <c r="D2" t="str">
+        <v>圖中是甚麼種類的動物？請選擇正確的分類：</v>
+      </c>
+      <c r="E2" t="str">
+        <v>鳥類</v>
+      </c>
+      <c r="F2" t="str">
+        <v>哺乳類</v>
+      </c>
+      <c r="G2" t="str">
+        <v>魚類</v>
+      </c>
+      <c r="H2" t="str">
+        <v>昆蟲</v>
+      </c>
+      <c r="I2" t="str">
+        <v>B</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>text-choice</v>
+      </c>
+      <c r="C3" t="str">
+        <v>光合作用</v>
+      </c>
+      <c r="D3" t="str">
+        <v>植物的哪個部分通常進行光合作用？</v>
+      </c>
+      <c r="E3" t="str">
+        <v>根</v>
+      </c>
+      <c r="F3" t="str">
+        <v>莖</v>
+      </c>
+      <c r="G3" t="str">
+        <v>葉</v>
+      </c>
+      <c r="H3" t="str">
+        <v>花</v>
+      </c>
+      <c r="I3" t="str">
+        <v>C</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>short-answer</v>
+      </c>
+      <c r="C4" t="str">
+        <v>水的蒸發</v>
+      </c>
+      <c r="D4" t="str">
+        <v>一杯水放在桌上，三天後水位變低了。水去哪裡了？請寫出你的想法。</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>text-choice</v>
+      </c>
+      <c r="C5" t="str">
+        <v>重力</v>
+      </c>
+      <c r="D5" t="str">
+        <v>下面哪一種力會把物體往地面拉？</v>
+      </c>
+      <c r="E5" t="str">
+        <v>磁力</v>
+      </c>
+      <c r="F5" t="str">
+        <v>摩擦力</v>
+      </c>
+      <c r="G5" t="str">
+        <v>重力</v>
+      </c>
+      <c r="H5" t="str">
+        <v>彈力</v>
+      </c>
+      <c r="I5" t="str">
+        <v>C</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>text-choice</v>
+      </c>
+      <c r="C6" t="str">
+        <v>魚類呼吸</v>
+      </c>
+      <c r="D6" t="str">
+        <v>魚類用什麼呼吸？</v>
+      </c>
+      <c r="E6" t="str">
+        <v>肺</v>
+      </c>
+      <c r="F6" t="str">
+        <v>皮膚</v>
+      </c>
+      <c r="G6" t="str">
+        <v>鰓</v>
+      </c>
+      <c r="H6" t="str">
+        <v>氣管</v>
+      </c>
+      <c r="I6" t="str">
+        <v>C</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>text-choice</v>
+      </c>
+      <c r="C7" t="str">
+        <v>自然資源</v>
+      </c>
+      <c r="D7" t="str">
+        <v>下列哪一個是「自然資源」？</v>
+      </c>
+      <c r="E7" t="str">
+        <v>塑膠</v>
+      </c>
+      <c r="F7" t="str">
+        <v>玻璃</v>
+      </c>
+      <c r="G7" t="str">
+        <v>陽光</v>
+      </c>
+      <c r="H7" t="str">
+        <v>鋼鐵</v>
+      </c>
+      <c r="I7" t="str">
+        <v>C</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>text-choice</v>
+      </c>
+      <c r="C8" t="str">
+        <v>太陽軌跡</v>
+      </c>
+      <c r="D8" t="str">
+        <v>一天中，太陽在天空中的位置怎樣變化？</v>
+      </c>
+      <c r="E8" t="str">
+        <v>從東邊升起，西邊落下</v>
+      </c>
+      <c r="F8" t="str">
+        <v>從西邊升起，東邊落下</v>
+      </c>
+      <c r="G8" t="str">
+        <v>一直停在頭頂</v>
+      </c>
+      <c r="H8" t="str">
+        <v>從北邊移到南邊</v>
+      </c>
+      <c r="I8" t="str">
+        <v>A</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>fill-blank</v>
+      </c>
+      <c r="C9" t="str">
+        <v>水的三態</v>
+      </c>
+      <c r="D9" t="str">
+        <v>水的三態分為固體、______ 和氣體。</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>液態</v>
+      </c>
+      <c r="J9" t="str">
+        <v>液態|液體</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>text-choice</v>
+      </c>
+      <c r="C10" t="str">
+        <v>昆蟲</v>
+      </c>
+      <c r="D10" t="str">
+        <v>下列哪一種動物是「昆蟲」？</v>
+      </c>
+      <c r="E10" t="str">
+        <v>蜘蛛</v>
+      </c>
+      <c r="F10" t="str">
+        <v>蜜蜂</v>
+      </c>
+      <c r="G10" t="str">
+        <v>蜈蚣</v>
+      </c>
+      <c r="H10" t="str">
+        <v>蝸牛</v>
+      </c>
+      <c r="I10" t="str">
+        <v>B</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>text-choice</v>
+      </c>
+      <c r="C11" t="str">
+        <v>雨衣材料</v>
+      </c>
+      <c r="D11" t="str">
+        <v>哪一種材料最適合用來做雨衣？</v>
+      </c>
+      <c r="E11" t="str">
+        <v>棉布</v>
+      </c>
+      <c r="F11" t="str">
+        <v>塑膠</v>
+      </c>
+      <c r="G11" t="str">
+        <v>紙</v>
+      </c>
+      <c r="H11" t="str">
+        <v>木頭</v>
+      </c>
+      <c r="I11" t="str">
+        <v>B</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>short-answer</v>
+      </c>
+      <c r="C12" t="str">
+        <v>月亮發光</v>
+      </c>
+      <c r="D12" t="str">
+        <v>月亮會發光嗎？請簡單說明。</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>text-choice</v>
+      </c>
+      <c r="C13" t="str">
+        <v>心臟</v>
+      </c>
+      <c r="D13" t="str">
+        <v>人體中負責傳送血液的器官是？</v>
+      </c>
+      <c r="E13" t="str">
+        <v>胃</v>
+      </c>
+      <c r="F13" t="str">
+        <v>心臟</v>
+      </c>
+      <c r="G13" t="str">
+        <v>肝臟</v>
+      </c>
+      <c r="H13" t="str">
+        <v>肺</v>
+      </c>
+      <c r="I13" t="str">
+        <v>B</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>text-choice</v>
+      </c>
+      <c r="C14" t="str">
+        <v>冰塊融化</v>
+      </c>
+      <c r="D14" t="str">
+        <v>冰塊放在室溫環境下會變成什麼？</v>
+      </c>
+      <c r="E14" t="str">
+        <v>水蒸氣</v>
+      </c>
+      <c r="F14" t="str">
+        <v>水</v>
+      </c>
+      <c r="G14" t="str">
+        <v>冰</v>
+      </c>
+      <c r="H14" t="str">
+        <v>霜</v>
+      </c>
+      <c r="I14" t="str">
+        <v>B</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>text-choice</v>
+      </c>
+      <c r="C15" t="str">
+        <v>草食動物</v>
+      </c>
+      <c r="D15" t="str">
+        <v>下列哪一項是草食性動物？</v>
+      </c>
+      <c r="E15" t="str">
+        <v>獅子</v>
+      </c>
+      <c r="F15" t="str">
+        <v>馬</v>
+      </c>
+      <c r="G15" t="str">
+        <v>老虎</v>
+      </c>
+      <c r="H15" t="str">
+        <v>狼</v>
+      </c>
+      <c r="I15" t="str">
+        <v>B</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>text-choice</v>
+      </c>
+      <c r="C16" t="str">
+        <v>颱風</v>
+      </c>
+      <c r="D16" t="str">
+        <v>在澳門，熱帶氣旋又被稱作甚麼？</v>
+      </c>
+      <c r="E16" t="str">
+        <v>暴雨</v>
+      </c>
+      <c r="F16" t="str">
+        <v>下雪</v>
+      </c>
+      <c r="G16" t="str">
+        <v>颱風</v>
+      </c>
+      <c r="H16" t="str">
+        <v>起霧</v>
+      </c>
+      <c r="I16" t="str">
+        <v>C</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>fill-blank</v>
+      </c>
+      <c r="C17" t="str">
+        <v>植物生長條件</v>
+      </c>
+      <c r="D17" t="str">
+        <v>一棵樹的生長需要哪些條件？寫出兩個。</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>陽光, 水</v>
+      </c>
+      <c r="J17" t="str">
+        <v>陽光|太陽|陽光空氣|水|水分|水份</v>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>text-choice</v>
+      </c>
+      <c r="C18" t="str">
+        <v>導電體</v>
+      </c>
+      <c r="D18" t="str">
+        <v>哪一個是導電體？</v>
+      </c>
+      <c r="E18" t="str">
+        <v>橡皮擦</v>
+      </c>
+      <c r="F18" t="str">
+        <v>鐵釘</v>
+      </c>
+      <c r="G18" t="str">
+        <v>塑膠尺</v>
+      </c>
+      <c r="H18" t="str">
+        <v>玻璃杯</v>
+      </c>
+      <c r="I18" t="str">
+        <v>B</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>text-choice</v>
+      </c>
+      <c r="C19" t="str">
+        <v>燃燒需要</v>
+      </c>
+      <c r="D19" t="str">
+        <v>蠟燭燃燒時，需要哪一種氣體？</v>
+      </c>
+      <c r="E19" t="str">
+        <v>二氧化碳</v>
+      </c>
+      <c r="F19" t="str">
+        <v>氧氣</v>
+      </c>
+      <c r="G19" t="str">
+        <v>氮氣</v>
+      </c>
+      <c r="H19" t="str">
+        <v>氫氣</v>
+      </c>
+      <c r="I19" t="str">
+        <v>B</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>text-choice</v>
+      </c>
+      <c r="C20" t="str">
+        <v>影子</v>
+      </c>
+      <c r="D20" t="str">
+        <v>什麼是「影子」形成的原因？</v>
+      </c>
+      <c r="E20" t="str">
+        <v>光線被物體擋住</v>
+      </c>
+      <c r="F20" t="str">
+        <v>物體自身發光</v>
+      </c>
+      <c r="G20" t="str">
+        <v>光線直接穿過物體</v>
+      </c>
+      <c r="H20" t="str">
+        <v>物體會變黑</v>
+      </c>
+      <c r="I20" t="str">
+        <v>A</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>short-answer</v>
+      </c>
+      <c r="C21" t="str">
+        <v>保護色</v>
+      </c>
+      <c r="D21" t="str">
+        <v>寫出一種具有「保護色」的動物。</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>text-choice</v>
+      </c>
+      <c r="C22" t="str">
+        <v>水星</v>
+      </c>
+      <c r="D22" t="str">
+        <v>下面哪一個行星離太陽最近？</v>
+      </c>
+      <c r="E22" t="str">
+        <v>地球</v>
+      </c>
+      <c r="F22" t="str">
+        <v>金星</v>
+      </c>
+      <c r="G22" t="str">
+        <v>水星</v>
+      </c>
+      <c r="H22" t="str">
+        <v>火星</v>
+      </c>
+      <c r="I22" t="str">
+        <v>C</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>text-choice</v>
+      </c>
+      <c r="C23" t="str">
+        <v>仙人掌</v>
+      </c>
+      <c r="D23" t="str">
+        <v>為甚麼仙人掌的葉子是尖刺狀？</v>
+      </c>
+      <c r="E23" t="str">
+        <v>減少營養流失</v>
+      </c>
+      <c r="F23" t="str">
+        <v>增加吸引空氣中水分的機會</v>
+      </c>
+      <c r="G23" t="str">
+        <v>減少水分流失</v>
+      </c>
+      <c r="H23" t="str">
+        <v>怕太陽曬</v>
+      </c>
+      <c r="I23" t="str">
+        <v>C</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K23"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/questions.xlsx
+++ b/questions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1217,9 +1217,44 @@
         <v/>
       </c>
     </row>
+    <row r="24">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>text-choice</v>
+      </c>
+      <c r="C24" t="str">
+        <v>測試</v>
+      </c>
+      <c r="D24" t="str">
+        <v>測試</v>
+      </c>
+      <c r="E24" t="str">
+        <v>減少營養流失</v>
+      </c>
+      <c r="F24" t="str">
+        <v>增加吸引空氣中水分的機會</v>
+      </c>
+      <c r="G24" t="str">
+        <v>減少水分流失</v>
+      </c>
+      <c r="H24" t="str">
+        <v>怕太陽曬</v>
+      </c>
+      <c r="I24" t="str">
+        <v>C</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K24"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/questions.xlsx
+++ b/questions.xlsx
@@ -479,7 +479,7 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>圖中是甚麼種類的動物？請選擇正確的分類：題目圖片</v>
       </c>
     </row>
     <row r="3">
